--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2489-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2489-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C9FD6D3-B507-482F-B2AF-ACFF550C9023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46A8745E-8E26-4D88-9C67-32E51D988EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{BFE21CF4-B165-4407-AC95-4181F36D5957}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{8EBDFBD0-F536-402A-9080-7263FA211DE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2489-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1511,26 +1511,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA84D08-5702-42AE-BF42-7F13DAB46B75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609D894B-B251-4462-9B4E-B09CA1EDAB0D}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1600,7 +1600,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1720,7 +1720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2022</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2021</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2020</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2019</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2018</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2017</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2016</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2015</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2014</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>2013</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2012</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>2011</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>2010</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36">
         <v>2009</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2008</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <v>2007</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>2006</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="36">
         <v>2005</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>2004</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="36">
         <v>2003</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>2002</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>9.92</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="36">
         <v>2001</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>2000</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="36">
         <v>1999</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>1998</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="36">
         <v>1997</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38" t="s">
         <v>57</v>
       </c>
